--- a/artfynd/A 49834-2021 artfynd.xlsx
+++ b/artfynd/A 49834-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124597768</v>
+        <v>124597842</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522235</v>
+        <v>522288</v>
       </c>
       <c r="R2" t="n">
-        <v>6641706</v>
+        <v>6641736</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -768,37 +769,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>eg trädbärande f d hagmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>trögväxande.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Acer platanoides # trögväxande.</t>
+          <t>inslag av asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124597842</v>
+        <v>124597768</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>79926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,27 +808,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -860,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522288</v>
+        <v>522235</v>
       </c>
       <c r="R3" t="n">
-        <v>6641736</v>
+        <v>6641706</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -910,12 +885,37 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>inslag av asp</t>
+          <t>eg trädbärande f d hagmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>trögväxande.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Acer platanoides # trögväxande.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 49834-2021 artfynd.xlsx
+++ b/artfynd/A 49834-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124597842</v>
+        <v>124597768</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>79926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522288</v>
+        <v>522235</v>
       </c>
       <c r="R2" t="n">
-        <v>6641736</v>
+        <v>6641706</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +768,37 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>inslag av asp</t>
+          <t>eg trädbärande f d hagmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>trögväxande.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Acer platanoides # trögväxande.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124597768</v>
+        <v>124597842</v>
       </c>
       <c r="B3" t="n">
-        <v>79926</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,26 +832,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522235</v>
+        <v>522288</v>
       </c>
       <c r="R3" t="n">
-        <v>6641706</v>
+        <v>6641736</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,37 +910,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>eg trädbärande f d hagmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>trögväxande.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Acer platanoides # trögväxande.</t>
+          <t>inslag av asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 49834-2021 artfynd.xlsx
+++ b/artfynd/A 49834-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124597842</v>
+        <v>124597768</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522288</v>
+        <v>522235</v>
       </c>
       <c r="R2" t="n">
-        <v>6641736</v>
+        <v>6641706</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +763,37 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>inslag av asp</t>
+          <t>eg trädbärande f d hagmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>trögväxande.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Acer platanoides # trögväxande.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124597768</v>
+        <v>124597842</v>
       </c>
       <c r="B3" t="n">
-        <v>79926</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,26 +822,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522235</v>
+        <v>522288</v>
       </c>
       <c r="R3" t="n">
-        <v>6641706</v>
+        <v>6641736</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,37 +900,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>eg trädbärande f d hagmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>trögväxande.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Acer platanoides # trögväxande.</t>
+          <t>inslag av asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 49834-2021 artfynd.xlsx
+++ b/artfynd/A 49834-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124597768</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,8 +930,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124597842</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>